--- a/Case Study #1 NovaTech Inc/hr_analysis.xlsx
+++ b/Case Study #1 NovaTech Inc/hr_analysis.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6160" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -51,13 +51,13 @@
     <t>Department</t>
   </si>
   <si>
-    <t>Average of salary_clean</t>
+    <t>Average Salary</t>
   </si>
   <si>
     <t>Joining Date</t>
   </si>
   <si>
-    <t>Count of Name</t>
+    <t>Headcount</t>
   </si>
   <si>
     <t>Finance</t>
@@ -84,7 +84,7 @@
     <t>Performance Score</t>
   </si>
   <si>
-    <t>Sum of salary_clean</t>
+    <t>Total Salary</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -4992,7 +4992,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="635" y="1771650"/>
-        <a:ext cx="4826000" cy="2743200"/>
+        <a:ext cx="4241800" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5021,8 +5021,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4972050" y="2717800"/>
-        <a:ext cx="4826000" cy="2743200"/>
+        <a:off x="4387850" y="2717800"/>
+        <a:ext cx="4356100" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5051,8 +5051,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10203815" y="2628900"/>
-        <a:ext cx="4337685" cy="2743200"/>
+        <a:off x="9149715" y="2628900"/>
+        <a:ext cx="3753485" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5081,8 +5081,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="14770100" y="4140200"/>
-        <a:ext cx="4826000" cy="2743200"/>
+        <a:off x="13131800" y="4140200"/>
+        <a:ext cx="4241800" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -22322,7 +22322,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of salary_clean" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="182"/>
+    <dataField name="Average Salary" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="182"/>
   </dataFields>
   <formats count="7">
     <format dxfId="0">
@@ -22441,7 +22441,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of salary_clean" fld="4" baseField="0" baseItem="0" numFmtId="182"/>
+    <dataField name="Total Salary" fld="4" baseField="0" baseItem="0" numFmtId="182"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1"/>
   <extLst>
@@ -22523,7 +22523,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of salary_clean" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="182"/>
+    <dataField name="Average Salary" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="182"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1"/>
   <extLst>
@@ -22613,7 +22613,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of salary_clean" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="182"/>
+    <dataField name="Average Salary" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="182"/>
   </dataFields>
   <formats count="5">
     <format dxfId="7">
@@ -22710,7 +22710,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Name" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Headcount" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStylePreset2_Accent1" showRowHeaders="1" showColHeaders="1"/>
   <extLst>
@@ -23021,15 +23021,15 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14.0909090909091"/>
-    <col min="2" max="2" width="22.6363636363636"/>
+    <col min="2" max="2" width="14.2727272727273"/>
     <col min="9" max="9" width="20.3636363636364"/>
-    <col min="10" max="10" width="19.1818181818182"/>
+    <col min="10" max="10" width="12.4545454545455"/>
     <col min="13" max="13" width="11.6363636363636"/>
-    <col min="14" max="14" width="22.6363636363636"/>
+    <col min="14" max="14" width="14.2727272727273"/>
     <col min="20" max="20" width="11.6363636363636"/>
-    <col min="21" max="21" width="22.6363636363636"/>
+    <col min="21" max="21" width="14.2727272727273"/>
     <col min="26" max="26" width="14"/>
-    <col min="27" max="27" width="14.7272727272727"/>
+    <col min="27" max="27" width="10.8181818181818"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:27">
